--- a/naver-place-crawler/results_health/북구_PT.xlsx
+++ b/naver-place-crawler/results_health/북구_PT.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피트온24 복현점</t>
+          <t>벨루스FIT&amp;PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mave000@naver.com</t>
+          <t>tizn_@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1322-3225</t>
+          <t>0507-1439-2551</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
+          <t>대구광역시 북구 동화천로 245 6층 604호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mave000</t>
+          <t>https://blog.naver.com/tizn_</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2016</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="n">
-        <v>889</v>
+        <v>57</v>
       </c>
       <c r="R2" t="n">
-        <v>2905</v>
+        <v>102</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1855565865</t>
+          <t>2076585284</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855565865</t>
+          <t>https://m.place.naver.com/place/2076585284</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BS피트니스</t>
+          <t>침산동 그룹PT 운동하는코끼리</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rwd1211@naver.com</t>
+          <t>oosotoo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>053-355-8080</t>
+          <t>0507-1403-3006</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호암로 28-3 4층</t>
+          <t>대구광역시 북구 침산남로 172 3층 운동하는 코끼리</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/oosotoo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>343</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1481477553</t>
+          <t>36123882</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481477553</t>
+          <t>https://m.place.naver.com/place/36123882</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바른마음체육관</t>
+          <t>모야짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sacheoncity@naver.com</t>
+          <t>greattae@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1365-0706</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 156 상가 지하 1층</t>
+          <t>대구광역시 북구 칠성로 25-22 모야짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brme0902?igsh=cWxxM3Y5NTRodzBi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +780,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,17 +801,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1845136410</t>
+          <t>1763678127</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845136410</t>
+          <t>https://m.place.naver.com/place/1763678127</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>패러다임짐 칠곡동천점</t>
+          <t>피트온24 복현점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>paradigm_cg@naver.com</t>
+          <t>mave000@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1379-5157</t>
+          <t>0507-1322-3225</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 6-1 2층</t>
+          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/paradigm_cg</t>
+          <t>https://blog.naver.com/mave000</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>108</v>
+        <v>2021</v>
       </c>
       <c r="Q5" t="n">
-        <v>312</v>
+        <v>984</v>
       </c>
       <c r="R5" t="n">
-        <v>420</v>
+        <v>3005</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +914,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1005890243</t>
+          <t>1855565865</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005890243</t>
+          <t>https://m.place.naver.com/place/1855565865</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>욱스짐 도남점 헬스PT</t>
+          <t>딜라이트 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>thenamja89@naver.com</t>
+          <t>delight_pt@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1329-3354</t>
+          <t>0507-1327-2806</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로8길 1 시그니쳐타워 7층 욱스짐</t>
+          <t>대구광역시 북구 매천로 124 2층 딜라이트 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wook_s_gym</t>
+          <t>https://blog.naver.com/delight_pt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>737</v>
+        <v>114</v>
       </c>
       <c r="Q6" t="n">
-        <v>216</v>
+        <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>953</v>
+        <v>135</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1008,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1340689579</t>
+          <t>1922976757</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340689579</t>
+          <t>https://m.place.naver.com/place/1922976757</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>위PT샵</t>
+          <t>어바웃더핏 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sdfgg110@naver.com</t>
+          <t>mildodrax2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1380-4960</t>
+          <t>0507-1314-2445</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 6 루가빌딩 3층</t>
+          <t>대구광역시 북구 학정로 149 태전동 1195 번지 4층, 어바웃더핏</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeba_2017ms.korea</t>
+          <t>https://www.instagram.com/aboutthefit_gym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>92</v>
+        <v>768</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="R7" t="n">
-        <v>107</v>
+        <v>905</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,46 +1102,46 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1564094440</t>
+          <t>1258524487</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564094440</t>
+          <t>https://m.place.naver.com/place/1258524487</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>심부름센터</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>대우흥신소사설탐정사무소심부름센터불륜증거미행사람찾기</t>
+          <t>산타나짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>koreadetective-@naver.com</t>
+          <t>qkrgkdms1993@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>070-5253-5450</t>
+          <t>0507-1388-4117</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태전동</t>
+          <t>대구광역시 북구 호국로 215 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1188,10 +1184,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1196,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1223084405</t>
+          <t>1920540468</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223084405</t>
+          <t>https://m.place.naver.com/place/1920540468</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피트낸스코리아</t>
+          <t>엔드짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>enrqorl88@naver.com</t>
+          <t>himy491@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1600-7178</t>
+          <t>053-311-6939</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 180</t>
+          <t>대구광역시 북구 매천로18길 29 5층, 엔드짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://fitnance.kr</t>
+          <t>https://www.instagram.com/endgym_official</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1290,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1785367820</t>
+          <t>1314145805</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785367820</t>
+          <t>https://m.place.naver.com/place/1314145805</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>크로스핏마즈</t>
+          <t>포레스트짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>zx95888@naver.com</t>
+          <t>forestgym-@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1311-3298</t>
+          <t>0507-1482-0831</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 144 화성투엠A동 지하1층</t>
+          <t>대구광역시 북구 칠성남로 43 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/marztraining</t>
+          <t>https://www.instagram.com/forestgym_/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="Q10" t="n">
-        <v>468</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>574</v>
+        <v>40</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>35720026</t>
+          <t>1186829756</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35720026</t>
+          <t>https://m.place.naver.com/place/1186829756</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,24 +1406,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>그린짐</t>
+          <t>BS피트니스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pk0236@naver.com</t>
+          <t>rwd1211@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1390-5563</t>
+          <t>053-355-8080</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 439 502호</t>
+          <t>대구광역시 북구 호암로 28-3 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1467,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1007068851</t>
+          <t>1481477553</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1007068851</t>
+          <t>https://m.place.naver.com/place/1481477553</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>벨루스FIT&amp;PT</t>
+          <t>플랜PT샵</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>tizn_@naver.com</t>
+          <t>dnwls6050@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1439-2551</t>
+          <t>0507-1439-8242</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동화천로 245 6층 604호</t>
+          <t>대구광역시 북구 학정로 430 3층 304 305호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tizn_</t>
+          <t>https://blog.naver.com/dnwls6050</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1557,17 +1553,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="Q12" t="n">
-        <v>56</v>
+        <v>234</v>
       </c>
       <c r="R12" t="n">
-        <v>97</v>
+        <v>340</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2076585284</t>
+          <t>1053211445</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076585284</t>
+          <t>https://m.place.naver.com/place/1053211445</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1598,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>더모스트핏</t>
+          <t>바른마음체육관</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>themostfit@naver.com</t>
+          <t>sacheoncity@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1323-4262</t>
+          <t>0507-1365-0706</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 173 시그니처타워 7층 더모스트핏</t>
+          <t>대구광역시 북구 동천로 156 상가 지하 1층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/themostfit_hyun</t>
+          <t>https://www.instagram.com/brme0902?igsh=cWxxM3Y5NTRodzBi</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1655,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,51 +1666,51 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1092605247</t>
+          <t>1845136410</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092605247</t>
+          <t>https://m.place.naver.com/place/1845136410</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>조지아 헬스 PT 스피닝 GX 칠곡점</t>
+          <t>크로스핏마즈</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gogia4879@naver.com</t>
+          <t>zx95888@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1383-4879</t>
+          <t>0507-1311-3298</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 133 701호,702호,703호</t>
+          <t>대구광역시 북구 침산로 144 화성투엠A동 지하1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/georgia.one1</t>
+          <t>https://www.instagram.com/marztraining</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1749,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>271</v>
+        <v>106</v>
       </c>
       <c r="Q14" t="n">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="R14" t="n">
-        <v>715</v>
+        <v>574</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,51 +1760,51 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1013813873</t>
+          <t>35720026</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013813873</t>
+          <t>https://m.place.naver.com/place/35720026</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>원나인피트니스 침산점</t>
+          <t>퀸스핏 1:1PT 센터</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>oneninegym_chimsan@naver.com</t>
+          <t>hotdogto@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1800-9533</t>
+          <t>0507-1378-1360</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 96 2층 201호</t>
+          <t>대구광역시 북구 학정동로 46 5층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oneninegym_chimsan</t>
+          <t>https://www.instagram.com/queensfit2013</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1823,7 +1819,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1843,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>353</v>
+        <v>9</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,51 +1854,47 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1682965261</t>
+          <t>31510477</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682965261</t>
+          <t>https://m.place.naver.com/place/31510477</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>버거짐</t>
+          <t>최코치필라테스&amp;피티</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>burgergym@naver.com</t>
+          <t>2gc1414@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1400-9556</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로 209 1층</t>
+          <t>대구광역시 북구 산격로 97 2층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/burger_gym_</t>
+          <t>https://www.instagram.com/choicoach2023</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1937,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="R16" t="n">
-        <v>513</v>
+        <v>85</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1590239180</t>
+          <t>1368752416</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1590239180</t>
+          <t>https://m.place.naver.com/place/1368752416</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1974,25 +1966,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>레드짐 VIP 산격점</t>
+          <t>더피지오랩 PT &amp; 재활 센터</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>redgym8555@naver.com</t>
+          <t>thephysiolab@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1372-7079</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>대구광역시 북구 검단로 9 2층 레드맥스VIP</t>
+          <t>대구광역시 북구 옥산로 95 205호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/redgym8555</t>
+          <t>https://blog.naver.com/thephysiolab</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2027,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="Q17" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="R17" t="n">
-        <v>218</v>
+        <v>98</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1699698590</t>
+          <t>1267989266</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699698590</t>
+          <t>https://m.place.naver.com/place/1267989266</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2064,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>바디웨이 헬스&amp;PT</t>
+          <t>원나인피트니스 침산점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>striver_ocean@naver.com</t>
+          <t>oneninegym_chimsan@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1488-2098</t>
+          <t>1800-9533</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로 148 4, 5층</t>
+          <t>대구광역시 북구 침산남로 96 2층 201호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/striver_ocean</t>
+          <t>https://blog.naver.com/oneninegym_chimsan</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2117,17 +2113,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>73</v>
+        <v>219</v>
       </c>
       <c r="Q18" t="n">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="R18" t="n">
-        <v>149</v>
+        <v>354</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,47 +2132,51 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1534494580</t>
+          <t>1682965261</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1534494580</t>
+          <t>https://m.place.naver.com/place/1682965261</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>레드워크아웃 헬스 &amp; PT</t>
+          <t>피티명가</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>siytg1234@naver.com</t>
+          <t>rhk2@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1324-1021</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로 127 4층,5층 레드워크아웃 (성화여고건너, 봄봄 건물)</t>
+          <t>대구광역시 북구 침산남로 153 3층 피티명가 (정호빌딩)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/siytg1234</t>
+          <t>http://instagram.com/ptmg153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>254</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>240</v>
+        <v>34</v>
       </c>
       <c r="R19" t="n">
-        <v>494</v>
+        <v>39</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,17 +2226,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1179762159</t>
+          <t>1618018901</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179762159</t>
+          <t>https://m.place.naver.com/place/1618018901</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2248,34 +2248,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>밸런스핏 PT&amp;필라테스</t>
+          <t>빅토리짐 운동센터</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>balancefit_pt@naver.com</t>
+          <t>sjsjfit@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1356-4983</t>
+          <t>053-325-8334</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 162-8 3층 밸런스핏</t>
+          <t>대구광역시 북구 학정로106길 18 2F 유산소 및 요가룸 3F 웨이트존</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_QIETxj/chat</t>
+          <t>https://www.instagram.com/victorygymofficial_</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2296,7 +2296,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>64</v>
+        <v>233</v>
       </c>
       <c r="Q20" t="n">
-        <v>112</v>
+        <v>478</v>
       </c>
       <c r="R20" t="n">
-        <v>176</v>
+        <v>711</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2320,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1569503169</t>
+          <t>1000816206</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569503169</t>
+          <t>https://m.place.naver.com/place/1000816206</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2342,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>바름PT&amp;피트니스</t>
+          <t>밸런스워킹PT 대구지사</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>baruemy@naver.com</t>
+          <t>damiano425@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1326-9724</t>
+          <t>053-311-5166</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경중앙로3길 21 라온하제 8층(1층에 CU있어요)</t>
+          <t>대구광역시 북구 칠곡중앙대로 500</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baruemy</t>
+          <t>https://blog.naver.com/damiano425</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>364</v>
+        <v>2</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,17 +2414,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1848126055</t>
+          <t>1169254360</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1848126055</t>
+          <t>https://m.place.naver.com/place/1169254360</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2436,29 +2436,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>점핑하이 칠곡점</t>
+          <t>위PT샵</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pkl0314@naver.com</t>
+          <t>sdfgg110@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1318-0956</t>
+          <t>0507-1380-4960</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 2 골든프라자 7층</t>
+          <t>대구광역시 북구 동천로23길 6 루가빌딩 3층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://instagram.com/jumping51130956</t>
+          <t>https://www.instagram.com/yeba_2017ms.korea</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="Q22" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="R22" t="n">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,56 +2508,56 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1136410767</t>
+          <t>1564094440</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136410767</t>
+          <t>https://m.place.naver.com/place/1564094440</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>밸런스워킹PT 대구지사</t>
+          <t>소마필라테스&amp;PT 복현점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>damiano425@naver.com</t>
+          <t>2379306@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>053-311-5166</t>
+          <t>0507-1494-2041</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 500</t>
+          <t>대구광역시 북구 복현로 34-1 2,3층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/damiano425</t>
+          <t>https://open.kakao.com/o/sVLSG6Jc</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2578,22 +2578,22 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>154</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>379</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2602,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1169254360</t>
+          <t>1434458798</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1169254360</t>
+          <t>https://m.place.naver.com/place/1434458798</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2624,29 +2624,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>이지피트니스</t>
+          <t>매드짐</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>easyfitness01@naver.com</t>
+          <t>csd828282@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1350-1029</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
+          <t>대구광역시 북구 연경지묘로 6 센텀타워 8층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/easyfitness01</t>
+          <t>https://blog.naver.com/csd828282</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2681,13 +2677,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>605</v>
+        <v>18</v>
       </c>
       <c r="Q24" t="n">
-        <v>283</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>888</v>
+        <v>32</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2692,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1129757069</t>
+          <t>1036138674</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129757069</t>
+          <t>https://m.place.naver.com/place/1036138674</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2718,29 +2714,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>국민피티 침산점</t>
+          <t>태고리즘 운동센터</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kukminpt@naver.com</t>
+          <t>gwgtaegorism@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1398-9797</t>
+          <t>0507-1471-1283</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구광역시 북구 학정로 551-50 4층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kukminpt</t>
+          <t>https://www.instagram.com/taegorism_rehab/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2775,13 +2771,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>697</v>
+        <v>47</v>
       </c>
       <c r="Q25" t="n">
-        <v>773</v>
+        <v>107</v>
       </c>
       <c r="R25" t="n">
-        <v>1470</v>
+        <v>154</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,17 +2786,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1636758988</t>
+          <t>1942933824</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636758988</t>
+          <t>https://m.place.naver.com/place/1942933824</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2812,29 +2808,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>피티명가</t>
+          <t>스타트 PT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rhk2@naver.com</t>
+          <t>startpt6260@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1324-1021</t>
+          <t>0507-1374-6260</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 153 3층 피티명가 (정호빌딩)</t>
+          <t>대구광역시 북구 대현남로 41 3층 302호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://instagram.com/ptmg153</t>
+          <t>https://www.instagram.com/start_pt6260</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2869,13 +2865,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R26" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,61 +2880,61 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1618018901</t>
+          <t>1981809419</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618018901</t>
+          <t>https://m.place.naver.com/place/1981809419</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내체육관</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>슬릭부스트 대구칠곡캠프</t>
+          <t>크로스핏 벨즈 칠곡</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ajdajddl5@naver.com</t>
+          <t>crossfit_bells@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>053-326-5563</t>
+          <t>0507-1424-9955</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 439 503호</t>
+          <t>대구광역시 북구 구암로21길 6 지하1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://cafe.naver.com/crossfitbells/5?boardType=L</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2959,17 +2955,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="Q27" t="n">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="R27" t="n">
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,51 +2974,51 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1817392005</t>
+          <t>1344030973</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817392005</t>
+          <t>https://m.place.naver.com/place/1344030973</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>제이에스타운 퍼스널트레이닝센터</t>
+          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dran77@naver.com</t>
+          <t>body7677@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>053-354-9797</t>
+          <t>0507-1388-7681</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대구광역시 북구 옥산로 98 2F</t>
+          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bodyengineers_kr</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3032,7 +3028,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3053,17 +3049,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>12</v>
+        <v>1442</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>2051</v>
       </c>
       <c r="R28" t="n">
-        <v>17</v>
+        <v>3493</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,51 +3068,51 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1094798598</t>
+          <t>1961345457</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1094798598</t>
+          <t>https://m.place.naver.com/place/1961345457</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>지젤 칠곡점 헬스 PT GX 요가</t>
+          <t>비티비에스 PT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>giselle331704@naver.com</t>
+          <t>whgudfo64@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1321-6496</t>
+          <t>0507-1392-3331</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동암로 90 3층</t>
+          <t>대구광역시 북구 침산남로 172 6층 비티비에스</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
+          <t>https://blog.naver.com/whgudfo64</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3131,7 +3127,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3151,13 +3147,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1235</v>
+        <v>249</v>
       </c>
       <c r="Q29" t="n">
-        <v>538</v>
+        <v>324</v>
       </c>
       <c r="R29" t="n">
-        <v>1773</v>
+        <v>573</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,17 +3162,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1616049160</t>
+          <t>1999844382</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616049160</t>
+          <t>https://m.place.naver.com/place/1999844382</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3188,34 +3184,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>레드짐 복현오거리점 헬스 &amp; PT</t>
+          <t>욱스짐 도남점 헬스PT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>redgym8555@naver.com</t>
+          <t>thenamja89@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>053-1877-3632</t>
+          <t>0507-1329-3354</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대구광역시 북구 검단로 9 3층, 4층</t>
+          <t>대구광역시 북구 도남중앙로8길 1 시그니쳐타워 7층 욱스짐</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://litt.ly/redgym_b5</t>
+          <t>https://www.instagram.com/wook_s_gym</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3245,13 +3241,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>809</v>
+        <v>753</v>
       </c>
       <c r="Q30" t="n">
-        <v>660</v>
+        <v>219</v>
       </c>
       <c r="R30" t="n">
-        <v>1469</v>
+        <v>972</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,17 +3256,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1813814971</t>
+          <t>1340689579</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1813814971</t>
+          <t>https://m.place.naver.com/place/1340689579</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3282,34 +3278,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아더핏</t>
+          <t>사이즈핏</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>rudwns5159@naver.com</t>
+          <t>sizefitpt1989@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1377-5159</t>
+          <t>0507-1380-2027</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 북구 내곡로 71 303호</t>
+          <t>대구광역시 북구 칠곡중앙대로 291 펫마트 2층 PT전문 사이즈핏</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sk9gOCze</t>
+          <t>https://blog.naver.com/sizefitpt1989</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3319,7 +3315,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3330,7 +3326,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3339,13 +3335,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q31" t="n">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="R31" t="n">
-        <v>138</v>
+        <v>201</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,51 +3350,51 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1105478663</t>
+          <t>1347371484</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105478663</t>
+          <t>https://m.place.naver.com/place/1347371484</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>체육관</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>필승관 레슬링 구암점</t>
+          <t>피트파크짐 PT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>matargear@naver.com</t>
+          <t>seu0112@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1429-2135</t>
+          <t>0507-1349-8265</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로 148 5층</t>
+          <t>대구광역시 북구 침산로 168 엠브로타워 4층 407호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pilseungwan_wrestling_guam</t>
+          <t>https://www.instagram.com/fitparkgym?igsh=MzRlODBiNWFlZA==</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3433,13 +3429,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="R32" t="n">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3448,51 +3444,51 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1675479581</t>
+          <t>1036478329</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1675479581</t>
+          <t>https://m.place.naver.com/place/1036478329</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>더퍼스트 피트니스 칠곡점</t>
+          <t>로이짐 1:1 PT 침산점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>tffpceo10@naver.com</t>
+          <t>ejhis12@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1304-3714</t>
+          <t>0507-1426-1060</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 125 5층</t>
+          <t>대구광역시 북구 침산남로 157 4층 로이짐</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tffpceo10</t>
+          <t>https://blog.naver.com/ejhis12</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3527,13 +3523,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>308</v>
+        <v>173</v>
       </c>
       <c r="Q33" t="n">
-        <v>280</v>
+        <v>438</v>
       </c>
       <c r="R33" t="n">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3542,56 +3538,56 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1040934279</t>
+          <t>1637712306</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040934279</t>
+          <t>https://m.place.naver.com/place/1637712306</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>실내체육관</t>
+          <t>체육관</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>크로스핏 벨즈 칠곡</t>
+          <t>필승관 레슬링 구암점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>crossfit_bells@naver.com</t>
+          <t>matargear@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1424-9955</t>
+          <t>0507-1429-2135</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로21길 6 지하1층</t>
+          <t>대구광역시 북구 구암로 148 5층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/crossfitbells/5?boardType=L</t>
+          <t>https://www.instagram.com/pilseungwan_wrestling_guam</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3621,13 +3617,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="Q34" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3636,17 +3632,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1344030973</t>
+          <t>1675479581</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1344030973</t>
+          <t>https://m.place.naver.com/place/1675479581</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3658,29 +3654,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>레드짐 침산점 헬스&amp;스파</t>
+          <t>더퍼스트 피트니스 칠곡점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>redgym-chim@naver.com</t>
+          <t>tffpceo10@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1329-5605</t>
+          <t>0507-1304-3714</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 138 6층</t>
+          <t>대구광역시 북구 동천로 125 5층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/redgym_chimsan</t>
+          <t>https://blog.naver.com/tffpceo10</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3695,7 +3691,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3715,13 +3711,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>384</v>
+        <v>308</v>
       </c>
       <c r="Q35" t="n">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="R35" t="n">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3730,51 +3726,51 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1070126824</t>
+          <t>1040934279</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070126824</t>
+          <t>https://m.place.naver.com/place/1040934279</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>태고리즘 운동센터</t>
+          <t>대구피티클럽</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>gwgtaegorism@naver.com</t>
+          <t>pt9559626@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1471-1283</t>
+          <t>053-955-9626</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 551-50 4층</t>
+          <t>대구광역시 북구 서변로 65 2층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taegorism_rehab/</t>
+          <t>https://blog.naver.com/pt9559626</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3789,7 +3785,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3805,17 +3801,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="R36" t="n">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3824,47 +3820,51 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1942933824</t>
+          <t>31383389</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942933824</t>
+          <t>https://m.place.naver.com/place/31383389</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>더레드짐 헬스 &amp; PT</t>
+          <t>아고게퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>thered_gym@naver.com</t>
+          <t>yun79e@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1385-0014</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로 105 태왕아너스상가 4층, 5층</t>
+          <t>대구광역시 북구 호국로 223 부국빌딩 5층 아고게 퍼스널 트레이닝</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/theredgym</t>
+          <t>https://blog.naver.com/yun79e</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>630</v>
+        <v>5</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3914,51 +3914,51 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1243559985</t>
+          <t>13201387</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243559985</t>
+          <t>https://m.place.naver.com/place/13201387</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>퀸스핏 1:1PT 센터</t>
+          <t>지젤 칠곡점 헬스 PT GX 요가</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hotdogto@naver.com</t>
+          <t>giselle331704@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1378-1360</t>
+          <t>0507-1321-6496</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정동로 46 5층</t>
+          <t>대구광역시 북구 동암로 90 3층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/queensfit2013</t>
+          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3993,13 +3993,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>1241</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>544</v>
       </c>
       <c r="R38" t="n">
-        <v>9</v>
+        <v>1785</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,51 +4008,51 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>31510477</t>
+          <t>1616049160</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31510477</t>
+          <t>https://m.place.naver.com/place/1616049160</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>대구피티클럽</t>
+          <t>메이크PT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pt9559626@naver.com</t>
+          <t>make_pt@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>053-955-9626</t>
+          <t>0507-1395-0708</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 북구 서변로 65 2층</t>
+          <t>대구광역시 북구 연경지묘로 2 7층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pt9559626</t>
+          <t>https://www.instagram.com/make_pt2022</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4083,17 +4083,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,56 +4102,56 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>31383389</t>
+          <t>1709497798</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31383389</t>
+          <t>https://m.place.naver.com/place/1709497798</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>스프라우트핏 여성전용 헬스&amp;PT</t>
+          <t>인스타퍼스널트레이닝 PT 침산점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sproutfit_@naver.com</t>
+          <t>instarpt2019@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1402-8161</t>
+          <t>0507-1345-9210</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 10 4층</t>
+          <t>대구광역시 북구 침산남로 165 5층 인스타퍼스널트레이닝 PT 침산점</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_Kpyxin?fbclid</t>
+          <t>https://blog.naver.com/instarpt2019</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4172,7 +4172,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4181,13 +4181,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>87</v>
+        <v>190</v>
       </c>
       <c r="Q40" t="n">
-        <v>114</v>
+        <v>600</v>
       </c>
       <c r="R40" t="n">
-        <v>201</v>
+        <v>790</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,17 +4196,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2039687494</t>
+          <t>1174523938</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039687494</t>
+          <t>https://m.place.naver.com/place/1174523938</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4218,34 +4218,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>오짐 헬스&amp;PT 동천점</t>
+          <t>지젤 노원점 헬스 PT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>forever7582@naver.com</t>
+          <t>giselle331709@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1421-9655</t>
+          <t>0507-1342-7936</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 125-4 4층 오짐 헬스&amp;PT</t>
+          <t>대구광역시 북구 팔달로35길 20 5층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://m.site.naver.com/1CMKz</t>
+          <t>https://blog.naver.com/giselle331709</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4275,13 +4275,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>308</v>
+        <v>474</v>
       </c>
       <c r="Q41" t="n">
-        <v>656</v>
+        <v>494</v>
       </c>
       <c r="R41" t="n">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,51 +4290,47 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1264751882</t>
+          <t>1294730549</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264751882</t>
+          <t>https://m.place.naver.com/place/1294730549</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>사이즈핏</t>
+          <t>레드워크아웃 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sizefitpt1989@naver.com</t>
+          <t>siytg1234@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0507-1380-2027</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 291 펫마트 2층 PT전문 사이즈핏</t>
+          <t>대구광역시 북구 복현로 127 4층,5층 레드워크아웃 (성화여고건너, 봄봄 건물)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sizefitpt1989</t>
+          <t>https://blog.naver.com/siytg1234</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4369,13 +4365,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>19</v>
+        <v>255</v>
       </c>
       <c r="Q42" t="n">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="R42" t="n">
-        <v>199</v>
+        <v>496</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,56 +4380,56 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1347371484</t>
+          <t>1179762159</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1347371484</t>
+          <t>https://m.place.naver.com/place/1179762159</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>레드짐 복싱</t>
+          <t>스톤짐 복현점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dietboxing@naver.com</t>
+          <t>stonegym_3@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1420-0305</t>
+          <t>0507-1333-5469</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로32길 2</t>
+          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dietboxing</t>
+          <t>http://pf.kakao.com/_pQdrxj</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4443,7 +4439,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4454,22 +4450,22 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>9</v>
+        <v>714</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>175</v>
       </c>
       <c r="R43" t="n">
-        <v>10</v>
+        <v>889</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4478,56 +4474,56 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>32762709</t>
+          <t>1113466448</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32762709</t>
+          <t>https://m.place.naver.com/place/1113466448</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>포레스트짐 헬스&amp;PT</t>
+          <t>아더핏</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>forestgym-@naver.com</t>
+          <t>rudwns5159@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1482-0831</t>
+          <t>0507-1377-5159</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성남로 43 2층</t>
+          <t>대구광역시 북구 내곡로 71 303호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forestgym_/</t>
+          <t>https://open.kakao.com/o/sk9gOCze</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4548,7 +4544,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4557,13 +4553,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q44" t="n">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="R44" t="n">
-        <v>40</v>
+        <v>138</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4572,17 +4568,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1186829756</t>
+          <t>1105478663</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186829756</t>
+          <t>https://m.place.naver.com/place/1105478663</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4594,34 +4590,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>플랜PT샵</t>
+          <t>밸런스핏 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dnwls6050@naver.com</t>
+          <t>balancefit_pt@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1439-8242</t>
+          <t>0507-1356-4983</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 430 3층 304 305호</t>
+          <t>대구광역시 북구 침산로 162-8 3층 밸런스핏</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dnwls6050</t>
+          <t>http://pf.kakao.com/_QIETxj/chat</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4631,7 +4627,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4642,7 +4638,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4651,13 +4647,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="Q45" t="n">
-        <v>231</v>
+        <v>112</v>
       </c>
       <c r="R45" t="n">
-        <v>334</v>
+        <v>176</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4666,51 +4662,51 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1053211445</t>
+          <t>1569503169</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053211445</t>
+          <t>https://m.place.naver.com/place/1569503169</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>산타나짐</t>
+          <t>버거짐</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>qkrgkdms1993@naver.com</t>
+          <t>burgergym@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1388-4117</t>
+          <t>0507-1400-9556</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호국로 215 4층</t>
+          <t>대구광역시 북구 팔달로 209 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/burger_gym_</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4720,7 +4716,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4741,17 +4737,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>362</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>517</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4760,47 +4756,51 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1920540468</t>
+          <t>1590239180</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920540468</t>
+          <t>https://m.place.naver.com/place/1590239180</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>매드짐</t>
+          <t>바름PT&amp;피트니스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>csd828282@naver.com</t>
+          <t>baruemy@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1326-9724</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경지묘로 6 센텀타워 8층</t>
+          <t>대구광역시 북구 연경중앙로3길 21 라온하제 8층(1층에 CU있어요)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/csd828282</t>
+          <t>https://blog.naver.com/baruemy/224250926219</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4835,13 +4835,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>18</v>
+        <v>252</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="R47" t="n">
-        <v>32</v>
+        <v>370</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4850,17 +4850,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1036138674</t>
+          <t>1848126055</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036138674</t>
+          <t>https://m.place.naver.com/place/1848126055</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4872,34 +4872,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>빅토리짐 PT&amp;헬스 동천점</t>
+          <t>오짐 헬스&amp;PT 동천점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sjsjfit@naver.com</t>
+          <t>forever7582@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1370-1301</t>
+          <t>0507-1421-9655</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 36 2층 201호</t>
+          <t>대구광역시 북구 동천로 125-4 4층 오짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sjsjfit</t>
+          <t>https://m.site.naver.com/1CMKz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4929,13 +4929,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>99</v>
+        <v>307</v>
       </c>
       <c r="Q48" t="n">
-        <v>188</v>
+        <v>657</v>
       </c>
       <c r="R48" t="n">
-        <v>287</v>
+        <v>964</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4944,51 +4944,51 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1903714032</t>
+          <t>1264751882</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1903714032</t>
+          <t>https://m.place.naver.com/place/1264751882</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>심부름센터</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>필라테스봄앤피티</t>
+          <t>대우흥신소사설탐정사무소심부름센터불륜증거미행사람찾기</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>pilatesbom8275@naver.com</t>
+          <t>koreadetective-@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1374-8314</t>
+          <t>070-5253-5450</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 551-50 대학당약국 건물 3층, 4층</t>
+          <t>대구광역시 북구 태전동</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilatesbom8275</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5038,51 +5038,47 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1470109452</t>
+          <t>1223084405</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1470109452</t>
+          <t>https://m.place.naver.com/place/1223084405</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>스타트 PT</t>
+          <t>더레드짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>startpt6260@naver.com</t>
+          <t>thered_gym@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1374-6260</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대현남로 41 3층 302호</t>
+          <t>대구광역시 북구 복현로 105 태왕아너스상가 4층, 5층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/start_pt6260</t>
+          <t>https://www.instagram.com/theredgym</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5117,13 +5113,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>19</v>
+        <v>472</v>
       </c>
       <c r="Q50" t="n">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="R50" t="n">
-        <v>46</v>
+        <v>630</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5132,51 +5128,51 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1981809419</t>
+          <t>1243559985</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1981809419</t>
+          <t>https://m.place.naver.com/place/1243559985</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>어바웃더핏 헬스 &amp; PT</t>
+          <t>우아해짐헬스PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mildodrax2@naver.com</t>
+          <t>tjdbs83@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1314-2445</t>
+          <t>0507-1316-1135</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 149 태전동 1195 번지 4층, 어바웃더핏</t>
+          <t>대구광역시 북구 동천로 127 5층 우아해짐&amp;필라테스</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aboutthefit_gym</t>
+          <t>https://blog.naver.com/tjdbs83</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5191,7 +5187,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5202,22 +5198,22 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>763</v>
+        <v>86</v>
       </c>
       <c r="Q51" t="n">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="R51" t="n">
-        <v>898</v>
+        <v>313</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5226,47 +5222,51 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1258524487</t>
+          <t>1145589800</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258524487</t>
+          <t>https://m.place.naver.com/place/1145589800</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>최코치필라테스&amp;피티</t>
+          <t>골든피티</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2gc1414@naver.com</t>
+          <t>rhfemsvlxl@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1344-4879</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>대구광역시 북구 산격로 97 2층</t>
+          <t>대구광역시 북구 내곡로 30 401호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/choicoach2023</t>
+          <t>https://www.instagram.com/golden.pt_</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5304,10 +5304,10 @@
         <v>5</v>
       </c>
       <c r="Q52" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="R52" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5316,17 +5316,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1368752416</t>
+          <t>1528721893</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1368752416</t>
+          <t>https://m.place.naver.com/place/1528721893</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5338,29 +5338,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>딜라이트 퍼스널트레이닝</t>
+          <t>아트라인 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>delight_pt@naver.com</t>
+          <t>art_line_pt@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1327-2806</t>
+          <t>0507-1369-2929</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매천로 124 2층 딜라이트 퍼스널트레이닝</t>
+          <t>대구광역시 북구 팔거천동로 206 2, 3층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/delight_pt</t>
+          <t>https://blog.naver.com/art_line_pt</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5395,13 +5395,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="Q53" t="n">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="R53" t="n">
-        <v>134</v>
+        <v>252</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5410,17 +5410,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1922976757</t>
+          <t>34079230</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1922976757</t>
+          <t>https://m.place.naver.com/place/34079230</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5432,29 +5432,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JH스포츠재활센터</t>
+          <t>피트낸스코리아</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>toughwogh@naver.com</t>
+          <t>enrqorl88@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>053-325-2132</t>
+          <t>1600-7178</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대천로 93 덕영빌딩 5층 501호</t>
+          <t>대구광역시 북구 칠곡중앙대로 180</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/toughwogh</t>
+          <t>http://fitnance.kr</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5492,10 +5492,10 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5504,17 +5504,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>33666439</t>
+          <t>1785367820</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33666439</t>
+          <t>https://m.place.naver.com/place/1785367820</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5526,29 +5526,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
+          <t>피트온24 칠곡점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>body7677@naver.com</t>
+          <t>fitness240@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1388-7681</t>
+          <t>053-313-8817</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
+          <t>대구광역시 북구 학정로 416 4층 피트온24</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodyengineers_kr</t>
+          <t>https://blog.naver.com/fitness240</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5574,7 +5574,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5583,13 +5583,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1433</v>
+        <v>2309</v>
       </c>
       <c r="Q55" t="n">
-        <v>1914</v>
+        <v>976</v>
       </c>
       <c r="R55" t="n">
-        <v>3347</v>
+        <v>3285</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5598,17 +5598,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1961345457</t>
+          <t>1175448883</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1961345457</t>
+          <t>https://m.place.naver.com/place/1175448883</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5620,29 +5620,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>로이짐 1:1 PT 침산점</t>
+          <t>마이송 피트니스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ejhis12@naver.com</t>
+          <t>dzosel@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1426-1060</t>
+          <t>0507-1364-7153</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 157 4층 로이짐</t>
+          <t>대구광역시 북구 동북로 247 상가동 211호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ejhis12</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5673,17 +5673,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="Q56" t="n">
-        <v>435</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>607</v>
+        <v>10</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5692,51 +5692,51 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1637712306</t>
+          <t>1435987015</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1637712306</t>
+          <t>https://m.place.naver.com/place/1435987015</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>마인드휘트니스 도남점</t>
+          <t>에이블리 PT센터</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mindfitness21@naver.com</t>
+          <t>tlsrms321@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1490-0792</t>
+          <t>0507-1321-0018</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로7길 20-4 601호</t>
+          <t>대구광역시 북구 칠곡중앙대로 527 3층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness21</t>
+          <t>https://www.instagram.com/ably_ptct</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5771,13 +5771,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>821</v>
+        <v>34</v>
       </c>
       <c r="Q57" t="n">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="R57" t="n">
-        <v>1070</v>
+        <v>136</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5786,51 +5786,51 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1552558325</t>
+          <t>1508796529</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1552558325</t>
+          <t>https://m.place.naver.com/place/1508796529</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>빅토리짐 운동센터</t>
+          <t>아이디짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sjsjfit@naver.com</t>
+          <t>ildomin@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>053-325-8334</t>
+          <t>0507-1319-9446</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로106길 18 2F 유산소 및 요가룸 3F 웨이트존</t>
+          <t>대구광역시 북구 내곡로 73 금강프라자 3층 아이디헬스IDGYM</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/victorygymofficial_</t>
+          <t>https://www.instagram.com/idgym24h?igsh=MTBnOHl0a2M3enBxdQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5856,7 +5856,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5865,13 +5865,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>233</v>
+        <v>74</v>
       </c>
       <c r="Q58" t="n">
-        <v>375</v>
+        <v>135</v>
       </c>
       <c r="R58" t="n">
-        <v>608</v>
+        <v>209</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5880,56 +5880,56 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1000816206</t>
+          <t>1254581921</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1000816206</t>
+          <t>https://m.place.naver.com/place/1254581921</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>소마필라테스&amp;PT 복현점</t>
+          <t>점핑하이 칠곡점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2379306@naver.com</t>
+          <t>pkl0314@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1494-2041</t>
+          <t>0507-1318-0956</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로 34-1 2,3층</t>
+          <t>대구광역시 북구 동천로23길 2 골든프라자 7층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sVLSG6Jc</t>
+          <t>http://instagram.com/jumping51130956</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5950,7 +5950,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5959,13 +5959,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>223</v>
+        <v>12</v>
       </c>
       <c r="Q59" t="n">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="R59" t="n">
-        <v>373</v>
+        <v>63</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5974,51 +5974,51 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1434458798</t>
+          <t>1136410767</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434458798</t>
+          <t>https://m.place.naver.com/place/1136410767</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>에이블리 PT센터</t>
+          <t>조지아 헬스 PT 스피닝 GX 칠곡점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>tlsrms321@naver.com</t>
+          <t>gogia4879@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1321-0018</t>
+          <t>0507-1383-4879</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 527 3층</t>
+          <t>대구광역시 북구 동천로 133 701호,702호,703호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ably_ptct</t>
+          <t>https://www.instagram.com/georgia.one1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6053,13 +6053,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>34</v>
+        <v>273</v>
       </c>
       <c r="Q60" t="n">
-        <v>102</v>
+        <v>446</v>
       </c>
       <c r="R60" t="n">
-        <v>136</v>
+        <v>719</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6068,17 +6068,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1508796529</t>
+          <t>1013813873</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1508796529</t>
+          <t>https://m.place.naver.com/place/1013813873</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6090,29 +6090,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>피트온24 칠곡점</t>
+          <t>그린짐</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>fitness240@naver.com</t>
+          <t>pk0236@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>053-313-8817</t>
+          <t>0507-1390-5563</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 416 4층 피트온24</t>
+          <t>대구광역시 북구 학정로 439 502호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitness240</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6138,22 +6138,22 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2303</v>
+        <v>23</v>
       </c>
       <c r="Q61" t="n">
-        <v>879</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
-        <v>3182</v>
+        <v>28</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6162,51 +6162,51 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1175448883</t>
+          <t>1007068851</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1175448883</t>
+          <t>https://m.place.naver.com/place/1007068851</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>S점핑다이어트</t>
+          <t>레드짐 침산점 헬스&amp;스파</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>zz13213@naver.com</t>
+          <t>redgym-chim@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1315-6161</t>
+          <t>0507-1329-5605</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대천로18길 1 4층</t>
+          <t>대구광역시 북구 침산로 138 6층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/redgym_chimsan</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6237,17 +6237,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>13</v>
+        <v>394</v>
       </c>
       <c r="Q62" t="n">
-        <v>134</v>
+        <v>224</v>
       </c>
       <c r="R62" t="n">
-        <v>147</v>
+        <v>618</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6256,17 +6256,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1122446650</t>
+          <t>1070126824</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1122446650</t>
+          <t>https://m.place.naver.com/place/1070126824</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6278,25 +6278,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>모야짐</t>
+          <t>더모스트핏</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>greattae@naver.com</t>
+          <t>themostfit@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1323-4262</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성로 25-22 모야짐</t>
+          <t>대구광역시 북구 침산로 173 시그니처타워 7층 더모스트핏</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/themostfit_hyun</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6306,7 +6310,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6327,17 +6331,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="R63" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6346,17 +6350,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1763678127</t>
+          <t>1092605247</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1763678127</t>
+          <t>https://m.place.naver.com/place/1092605247</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6368,29 +6372,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>아이디짐 헬스&amp;PT</t>
+          <t>바디채널 침산점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ildomin@naver.com</t>
+          <t>bodycs@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1319-9446</t>
+          <t>0507-1342-4850</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>대구광역시 북구 내곡로 73 금강프라자 3층 아이디헬스IDGYM</t>
+          <t>대구광역시 북구 침산남로 154 10층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/idgym24h?igsh=MTBnOHl0a2M3enBxdQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/bodychannel_chimsan</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6416,7 +6420,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6425,13 +6429,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>73</v>
+        <v>177</v>
       </c>
       <c r="Q64" t="n">
-        <v>135</v>
+        <v>1529</v>
       </c>
       <c r="R64" t="n">
-        <v>208</v>
+        <v>1706</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6440,17 +6444,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1254581921</t>
+          <t>1023076989</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1254581921</t>
+          <t>https://m.place.naver.com/place/1023076989</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6462,29 +6466,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>침산동 그룹PT 운동하는코끼리</t>
+          <t>제이에스타운 퍼스널트레이닝센터</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>oosotoo@naver.com</t>
+          <t>dran77@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1403-3006</t>
+          <t>053-354-9797</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 172 3층 운동하는 코끼리</t>
+          <t>대구광역시 북구 옥산로 98 2F</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oosotoo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6494,12 +6498,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6515,17 +6519,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>180</v>
+        <v>12</v>
       </c>
       <c r="Q65" t="n">
-        <v>163</v>
+        <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>343</v>
+        <v>17</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6534,56 +6538,56 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>36123882</t>
+          <t>1094798598</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36123882</t>
+          <t>https://m.place.naver.com/place/1094798598</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>스톤짐 복현점</t>
+          <t>필라테스봄앤피티</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>stonegym_3@naver.com</t>
+          <t>pilatesbom8275@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1333-5469</t>
+          <t>0507-1374-8314</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
+          <t>대구광역시 북구 학정로 551-50 대학당약국 건물 3층, 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pQdrxj</t>
+          <t>https://blog.naver.com/pilatesbom8275</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6593,7 +6597,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6604,7 +6608,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6613,13 +6617,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>703</v>
+        <v>42</v>
       </c>
       <c r="Q66" t="n">
         <v>173</v>
       </c>
       <c r="R66" t="n">
-        <v>876</v>
+        <v>215</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6628,17 +6632,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1113466448</t>
+          <t>1470109452</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113466448</t>
+          <t>https://m.place.naver.com/place/1470109452</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6650,29 +6654,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>아트라인 퍼스널트레이닝</t>
+          <t>슬릭부스트 대구칠곡캠프</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>art_line_pt@naver.com</t>
+          <t>ajdajddl5@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1369-2929</t>
+          <t>053-326-5563</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로 206 2, 3층</t>
+          <t>대구광역시 북구 학정로 439 503호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/art_line_pt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6682,12 +6686,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6703,17 +6707,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q67" t="n">
-        <v>169</v>
+        <v>26</v>
       </c>
       <c r="R67" t="n">
-        <v>251</v>
+        <v>107</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6722,17 +6726,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>34079230</t>
+          <t>1817392005</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34079230</t>
+          <t>https://m.place.naver.com/place/1817392005</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6744,29 +6748,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>우아해짐헬스PT&amp;필라테스</t>
+          <t>레드짐 VIP 산격점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>tjdbs83@naver.com</t>
+          <t>redgym8555@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1316-1135</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 127 5층 우아해짐&amp;필라테스</t>
+          <t>대구광역시 북구 검단로 9 2층 레드맥스VIP</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjdbs83</t>
+          <t>https://blog.naver.com/redgym8555</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6797,17 +6797,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="Q68" t="n">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="R68" t="n">
-        <v>311</v>
+        <v>218</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6816,51 +6816,51 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1145589800</t>
+          <t>1699698590</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145589800</t>
+          <t>https://m.place.naver.com/place/1699698590</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>아고게퍼스널트레이닝</t>
+          <t>이지피트니스</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>yun79e@naver.com</t>
+          <t>easyfitness01@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1385-0014</t>
+          <t>0507-1350-1029</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호국로 223 부국빌딩 5층 아고게 퍼스널 트레이닝</t>
+          <t>대구광역시 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yun79e</t>
+          <t>https://blog.naver.com/easyfitness01</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6891,17 +6891,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>605</v>
       </c>
       <c r="Q69" t="n">
-        <v>5</v>
+        <v>286</v>
       </c>
       <c r="R69" t="n">
-        <v>5</v>
+        <v>891</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6910,56 +6910,56 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>13201387</t>
+          <t>1129757069</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13201387</t>
+          <t>https://m.place.naver.com/place/1129757069</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>피트파크짐 PT</t>
+          <t>스프라우트핏 여성전용 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>seu0112@naver.com</t>
+          <t>sproutfit_@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1349-8265</t>
+          <t>0507-1402-8161</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 168 엠브로타워 4층 407호</t>
+          <t>대구광역시 북구 동천로23길 10 4층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitparkgym?igsh=MzRlODBiNWFlZA==</t>
+          <t>https://pf.kakao.com/_Kpyxin?fbclid</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6980,7 +6980,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6989,13 +6989,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="Q70" t="n">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="R70" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7004,51 +7004,51 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1036478329</t>
+          <t>2039687494</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036478329</t>
+          <t>https://m.place.naver.com/place/2039687494</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>더피지오랩 PT &amp; 재활 센터</t>
+          <t>레드짐 복싱</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>thephysiolab@naver.com</t>
+          <t>dietboxing@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1372-7079</t>
+          <t>0507-1420-0305</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>대구광역시 북구 옥산로 95 205호</t>
+          <t>대구광역시 북구 침산로32길 2</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thephysiolab</t>
+          <t>https://blog.naver.com/dietboxing</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7079,17 +7079,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="Q71" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7098,56 +7098,56 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1267989266</t>
+          <t>32762709</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267989266</t>
+          <t>https://m.place.naver.com/place/32762709</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>메이크PT</t>
+          <t>레드짐 복현오거리점 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>make_pt@naver.com</t>
+          <t>redgym8555@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1395-0708</t>
+          <t>053-1877-3632</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경지묘로 2 7층</t>
+          <t>대구광역시 북구 검단로 9 3층, 4층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/make_pt2022</t>
+          <t>https://litt.ly/redgym_b5</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7177,13 +7177,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>662</v>
       </c>
       <c r="R72" t="n">
-        <v>4</v>
+        <v>1478</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7192,17 +7192,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1709497798</t>
+          <t>1813814971</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709497798</t>
+          <t>https://m.place.naver.com/place/1813814971</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7214,29 +7214,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>마이송 피트니스</t>
+          <t>빅토리짐 PT&amp;헬스 동천점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>dzosel@naver.com</t>
+          <t>sjsjfit@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1364-7153</t>
+          <t>0507-1370-1301</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 247 상가동 211호</t>
+          <t>대구광역시 북구 동천로23길 36 2층 201호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sjsjfit</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="R73" t="n">
-        <v>10</v>
+        <v>292</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7286,51 +7286,51 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1435987015</t>
+          <t>1903714032</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1435987015</t>
+          <t>https://m.place.naver.com/place/1903714032</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>골든피티</t>
+          <t>바디웨이 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>rhfemsvlxl@naver.com</t>
+          <t>striver_ocean@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1344-4879</t>
+          <t>0507-1488-2098</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>대구광역시 북구 내곡로 30 401호</t>
+          <t>대구광역시 북구 구암로 148 4, 5층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/golden.pt_</t>
+          <t>https://blog.naver.com/striver_ocean</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7361,17 +7361,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="Q74" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="R74" t="n">
-        <v>42</v>
+        <v>149</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7380,17 +7380,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1528721893</t>
+          <t>1534494580</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1528721893</t>
+          <t>https://m.place.naver.com/place/1534494580</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7402,29 +7402,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>인스타퍼스널트레이닝 PT 침산점</t>
+          <t>JH스포츠재활센터</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>instarpt2019@naver.com</t>
+          <t>toughwogh@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1345-9210</t>
+          <t>053-325-2132</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 165 5층 인스타퍼스널트레이닝 PT 침산점</t>
+          <t>대구광역시 북구 대천로 93 덕영빌딩 5층 501호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/instarpt2019</t>
+          <t>https://blog.naver.com/toughwogh</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7455,17 +7455,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>594</v>
+        <v>2</v>
       </c>
       <c r="R75" t="n">
-        <v>784</v>
+        <v>2</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7474,17 +7474,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1174523938</t>
+          <t>33666439</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174523938</t>
+          <t>https://m.place.naver.com/place/33666439</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7496,29 +7496,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>비티비에스 PT</t>
+          <t>국민피티 침산점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>whgudfo64@naver.com</t>
+          <t>kukminpt@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1392-3331</t>
+          <t>0507-1398-9797</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 172 6층 비티비에스</t>
+          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/whgudfo64</t>
+          <t>https://www.instagram.com/kukminpt</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7553,13 +7553,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>247</v>
+        <v>701</v>
       </c>
       <c r="Q76" t="n">
-        <v>319</v>
+        <v>1015</v>
       </c>
       <c r="R76" t="n">
-        <v>566</v>
+        <v>1716</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7568,17 +7568,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1999844382</t>
+          <t>1636758988</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999844382</t>
+          <t>https://m.place.naver.com/place/1636758988</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/북구_PT.xlsx
+++ b/naver-place-crawler/results_health/북구_PT.xlsx
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>벨루스FIT&amp;PT</t>
+          <t>스톤짐 복현점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tizn_@naver.com</t>
+          <t>stonegym_3@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1439-2551</t>
+          <t>0507-1333-5469</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동화천로 245 6층 604호</t>
+          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tizn_</t>
+          <t>http://pf.kakao.com/_pQdrxj</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,22 +612,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>45</v>
+        <v>717</v>
       </c>
       <c r="Q2" t="n">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="R2" t="n">
-        <v>102</v>
+        <v>897</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2076585284</t>
+          <t>1113466448</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076585284</t>
+          <t>https://m.place.naver.com/place/1113466448</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>침산동 그룹PT 운동하는코끼리</t>
+          <t>소마필라테스&amp;PT 복현점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oosotoo@naver.com</t>
+          <t>2379306@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1403-3006</t>
+          <t>0507-1494-2041</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 172 3층 운동하는 코끼리</t>
+          <t>대구광역시 북구 복현로 34-1 2,3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oosotoo</t>
+          <t>https://open.kakao.com/o/sVLSG6Jc</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="Q3" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="R3" t="n">
-        <v>343</v>
+        <v>383</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>36123882</t>
+          <t>1434458798</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36123882</t>
+          <t>https://m.place.naver.com/place/1434458798</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -752,25 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>모야짐</t>
+          <t>JH스포츠재활센터</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>greattae@naver.com</t>
+          <t>toughwogh@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>053-325-2132</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성로 25-22 모야짐</t>
+          <t>대구광역시 북구 대천로 93 덕영빌딩 5층 501호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/toughwogh</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -780,12 +784,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1763678127</t>
+          <t>33666439</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1763678127</t>
+          <t>https://m.place.naver.com/place/33666439</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피트온24 복현점</t>
+          <t>제이에스타운 퍼스널트레이닝센터</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mave000@naver.com</t>
+          <t>dran77@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1322-3225</t>
+          <t>053-354-9797</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
+          <t>대구광역시 북구 옥산로 98 2F</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mave000</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -874,12 +878,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -895,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2021</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>984</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>3005</v>
+        <v>17</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,51 +918,47 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1855565865</t>
+          <t>1094798598</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855565865</t>
+          <t>https://m.place.naver.com/place/1094798598</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>딜라이트 퍼스널트레이닝</t>
+          <t>최코치필라테스&amp;피티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>delight_pt@naver.com</t>
+          <t>2gc1414@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1327-2806</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매천로 124 2층 딜라이트 퍼스널트레이닝</t>
+          <t>대구광역시 북구 산격로 97 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/delight_pt</t>
+          <t>https://www.instagram.com/choicoach2023</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>114</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="R6" t="n">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1922976757</t>
+          <t>1368752416</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1922976757</t>
+          <t>https://m.place.naver.com/place/1368752416</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>어바웃더핏 헬스 &amp; PT</t>
+          <t>레드짐 침산점 헬스&amp;스파</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mildodrax2@naver.com</t>
+          <t>redgym-chim@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1314-2445</t>
+          <t>0507-1329-5605</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 149 태전동 1195 번지 4층, 어바웃더핏</t>
+          <t>대구광역시 북구 침산로 138 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aboutthefit_gym</t>
+          <t>https://www.instagram.com/redgym_chimsan</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1078,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>768</v>
+        <v>396</v>
       </c>
       <c r="Q7" t="n">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="R7" t="n">
-        <v>905</v>
+        <v>622</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1258524487</t>
+          <t>1070126824</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258524487</t>
+          <t>https://m.place.naver.com/place/1070126824</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>산타나짐</t>
+          <t>위PT샵</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>qkrgkdms1993@naver.com</t>
+          <t>sdfgg110@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1388-4117</t>
+          <t>0507-1380-4960</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호국로 215 4층</t>
+          <t>대구광역시 북구 동천로23길 6 루가빌딩 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/yeba_2017ms.korea</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,51 +1196,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1920540468</t>
+          <t>1564094440</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920540468</t>
+          <t>https://m.place.naver.com/place/1564094440</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엔드짐</t>
+          <t>아고게퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>himy491@naver.com</t>
+          <t>yun79e@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>053-311-6939</t>
+          <t>0507-1385-0014</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매천로18길 29 5층, 엔드짐</t>
+          <t>대구광역시 북구 호국로 223 부국빌딩 5층 아고게 퍼스널 트레이닝</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/endgym_official</t>
+          <t>https://blog.naver.com/yun79e</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,51 +1290,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1314145805</t>
+          <t>13201387</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314145805</t>
+          <t>https://m.place.naver.com/place/13201387</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>포레스트짐 헬스&amp;PT</t>
+          <t>바름PT&amp;피트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>forestgym-@naver.com</t>
+          <t>baruemy@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1482-0831</t>
+          <t>0507-1326-9724</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성남로 43 2층</t>
+          <t>대구광역시 북구 연경중앙로3길 21 라온하제 8층(1층에 CU있어요)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forestgym_/</t>
+          <t>https://blog.naver.com/baruemy/224250926219</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>253</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="R10" t="n">
-        <v>40</v>
+        <v>373</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1186829756</t>
+          <t>1848126055</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186829756</t>
+          <t>https://m.place.naver.com/place/1848126055</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BS피트니스</t>
+          <t>원나인피트니스 침산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rwd1211@naver.com</t>
+          <t>oneninegym_chimsan@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>053-355-8080</t>
+          <t>1800-9533</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호암로 28-3 4층</t>
+          <t>대구광역시 북구 침산남로 96 2층 201호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/oneninegym_chimsan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1459,17 +1459,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>356</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1481477553</t>
+          <t>1682965261</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481477553</t>
+          <t>https://m.place.naver.com/place/1682965261</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1500,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>플랜PT샵</t>
+          <t>슬릭부스트 대구칠곡캠프</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dnwls6050@naver.com</t>
+          <t>ajdajddl5@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1439-8242</t>
+          <t>053-326-5563</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 430 3층 304 305호</t>
+          <t>대구광역시 북구 학정로 439 503호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dnwls6050</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="Q12" t="n">
-        <v>234</v>
+        <v>26</v>
       </c>
       <c r="R12" t="n">
-        <v>340</v>
+        <v>107</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1053211445</t>
+          <t>1817392005</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053211445</t>
+          <t>https://m.place.naver.com/place/1817392005</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>바른마음체육관</t>
+          <t>플랜PT샵</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sacheoncity@naver.com</t>
+          <t>dnwls6050@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1365-0706</t>
+          <t>0507-1439-8242</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 156 상가 지하 1층</t>
+          <t>대구광역시 북구 학정로 430 3층 304 305호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brme0902?igsh=cWxxM3Y5NTRodzBi</t>
+          <t>https://blog.naver.com/dnwls6050</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>342</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1845136410</t>
+          <t>1053211445</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845136410</t>
+          <t>https://m.place.naver.com/place/1053211445</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1688,29 +1688,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>크로스핏마즈</t>
+          <t>메이크PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>zx95888@naver.com</t>
+          <t>make_pt@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1311-3298</t>
+          <t>0507-1395-0708</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 144 화성투엠A동 지하1층</t>
+          <t>대구광역시 북구 연경지묘로 2 7층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/marztraining</t>
+          <t>https://www.instagram.com/make_pt2022</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>468</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>574</v>
+        <v>4</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>35720026</t>
+          <t>1709497798</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35720026</t>
+          <t>https://m.place.naver.com/place/1709497798</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1782,29 +1782,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>퀸스핏 1:1PT 센터</t>
+          <t>에이블리 PT센터</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>hotdogto@naver.com</t>
+          <t>tlsrms321@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1378-1360</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정동로 46 5층</t>
+          <t>대구광역시 북구 칠곡중앙대로 527 3층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/queensfit2013</t>
+          <t>https://www.instagram.com/ably_ptct</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1839,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,47 +1850,51 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>31510477</t>
+          <t>1508796529</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31510477</t>
+          <t>https://m.place.naver.com/place/1508796529</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>심부름센터</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>최코치필라테스&amp;피티</t>
+          <t>대우흥신소사설탐정사무소심부름센터불륜증거미행사람찾기</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2gc1414@naver.com</t>
+          <t>koreadetective-@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>070-5253-5450</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대구광역시 북구 산격로 97 2층</t>
+          <t>대구광역시 북구 태전동</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/choicoach2023</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1925,17 +1925,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,51 +1944,51 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1368752416</t>
+          <t>1223084405</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1368752416</t>
+          <t>https://m.place.naver.com/place/1223084405</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>더피지오랩 PT &amp; 재활 센터</t>
+          <t>아이디짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>thephysiolab@naver.com</t>
+          <t>ildomin@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1372-7079</t>
+          <t>0507-1319-9446</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>대구광역시 북구 옥산로 95 205호</t>
+          <t>대구광역시 북구 내곡로 73 금강프라자 3층 아이디헬스IDGYM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thephysiolab</t>
+          <t>https://www.instagram.com/idgym24h?igsh=MTBnOHl0a2M3enBxdQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2014,7 +2014,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="Q17" t="n">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="R17" t="n">
-        <v>98</v>
+        <v>209</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,51 +2038,51 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1267989266</t>
+          <t>1254581921</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267989266</t>
+          <t>https://m.place.naver.com/place/1254581921</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>원나인피트니스 침산점</t>
+          <t>아더핏</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>oneninegym_chimsan@naver.com</t>
+          <t>rudwns5159@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1800-9533</t>
+          <t>0507-1377-5159</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 96 2층 201호</t>
+          <t>대구광역시 북구 내곡로 71 303호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oneninegym_chimsan</t>
+          <t>https://open.kakao.com/o/sk9gOCze</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2108,7 +2108,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>219</v>
+        <v>23</v>
       </c>
       <c r="Q18" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="R18" t="n">
-        <v>354</v>
+        <v>138</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,56 +2132,56 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1682965261</t>
+          <t>1105478663</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682965261</t>
+          <t>https://m.place.naver.com/place/1105478663</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>피티명가</t>
+          <t>스프라우트핏 여성전용 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rhk2@naver.com</t>
+          <t>sproutfit_@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1324-1021</t>
+          <t>0507-1402-8161</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 153 3층 피티명가 (정호빌딩)</t>
+          <t>대구광역시 북구 동천로23길 10 4층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://instagram.com/ptmg153</t>
+          <t>https://pf.kakao.com/_Kpyxin?fbclid</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2202,7 +2202,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="Q19" t="n">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="R19" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,51 +2226,51 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1618018901</t>
+          <t>2039687494</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618018901</t>
+          <t>https://m.place.naver.com/place/2039687494</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>빅토리짐 운동센터</t>
+          <t>BS피트니스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sjsjfit@naver.com</t>
+          <t>rwd1211@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>053-325-8334</t>
+          <t>053-355-8080</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로106길 18 2F 유산소 및 요가룸 3F 웨이트존</t>
+          <t>대구광역시 북구 호암로 28-3 4층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/victorygymofficial_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>478</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>711</v>
+        <v>6</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2320,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1000816206</t>
+          <t>1481477553</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1000816206</t>
+          <t>https://m.place.naver.com/place/1481477553</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2342,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>밸런스워킹PT 대구지사</t>
+          <t>태고리즘 운동센터</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>damiano425@naver.com</t>
+          <t>gwgtaegorism@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>053-311-5166</t>
+          <t>0507-1471-1283</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 500</t>
+          <t>대구광역시 북구 학정로 551-50 4층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/damiano425</t>
+          <t>https://www.instagram.com/taegorism_rehab/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,17 +2414,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1169254360</t>
+          <t>1942933824</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1169254360</t>
+          <t>https://m.place.naver.com/place/1942933824</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2436,29 +2436,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>위PT샵</t>
+          <t>빅토리짐 운동센터</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sdfgg110@naver.com</t>
+          <t>sjsjfit@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1380-4960</t>
+          <t>053-325-8334</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 6 루가빌딩 3층</t>
+          <t>대구광역시 북구 학정로106길 18 2F 유산소 및 요가룸 3F 웨이트존</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeba_2017ms.korea</t>
+          <t>https://www.instagram.com/victorygymofficial_</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>94</v>
+        <v>233</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>479</v>
       </c>
       <c r="R22" t="n">
-        <v>109</v>
+        <v>712</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,61 +2508,61 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1564094440</t>
+          <t>1000816206</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564094440</t>
+          <t>https://m.place.naver.com/place/1000816206</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>소마필라테스&amp;PT 복현점</t>
+          <t>산타나짐</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2379306@naver.com</t>
+          <t>sosu0512@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1494-2041</t>
+          <t>0507-1388-4117</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로 34-1 2,3층</t>
+          <t>대구광역시 북구 호국로 215 4층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sVLSG6Jc</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2578,22 +2578,22 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>379</v>
+        <v>1</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2602,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1434458798</t>
+          <t>1920540468</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434458798</t>
+          <t>https://m.place.naver.com/place/1920540468</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2624,25 +2624,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>매드짐</t>
+          <t>지젤 칠곡점 헬스 PT GX 요가</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>csd828282@naver.com</t>
+          <t>giselle331704@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1321-6496</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경지묘로 6 센텀타워 8층</t>
+          <t>대구광역시 북구 동암로 90 3층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/csd828282</t>
+          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2657,7 +2661,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2677,13 +2681,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>18</v>
+        <v>1244</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>544</v>
       </c>
       <c r="R24" t="n">
-        <v>32</v>
+        <v>1788</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2696,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1036138674</t>
+          <t>1616049160</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036138674</t>
+          <t>https://m.place.naver.com/place/1616049160</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2714,29 +2718,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>태고리즘 운동센터</t>
+          <t>아트라인 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>gwgtaegorism@naver.com</t>
+          <t>art_line_pt@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1471-1283</t>
+          <t>0507-1369-2929</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 551-50 4층</t>
+          <t>대구광역시 북구 팔거천동로 206 2, 3층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taegorism_rehab/</t>
+          <t>https://blog.naver.com/art_line_pt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2751,7 +2755,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2771,13 +2775,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="Q25" t="n">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="R25" t="n">
-        <v>154</v>
+        <v>253</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2790,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1942933824</t>
+          <t>34079230</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942933824</t>
+          <t>https://m.place.naver.com/place/34079230</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2808,29 +2812,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>스타트 PT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>startpt6260@naver.com</t>
-        </is>
-      </c>
+          <t>퀸스핏 1:1PT 센터</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1374-6260</t>
+          <t>0507-1378-1360</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대현남로 41 3층 302호</t>
+          <t>대구광역시 북구 학정동로 46 5층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/start_pt6260</t>
+          <t>https://www.instagram.com/queensfit2013</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2865,13 +2865,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,56 +2880,56 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1981809419</t>
+          <t>31510477</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1981809419</t>
+          <t>https://m.place.naver.com/place/31510477</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>실내체육관</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>크로스핏 벨즈 칠곡</t>
+          <t>밸런스워킹PT 대구지사</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>crossfit_bells@naver.com</t>
+          <t>damiano425@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1424-9955</t>
+          <t>053-311-5166</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로21길 6 지하1층</t>
+          <t>대구광역시 북구 칠곡중앙대로 500</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/crossfitbells/5?boardType=L</t>
+          <t>https://blog.naver.com/damiano425</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,51 +2974,51 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1344030973</t>
+          <t>1169254360</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1344030973</t>
+          <t>https://m.place.naver.com/place/1169254360</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>실내체육관</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
+          <t>크로스핏 벨즈 칠곡</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>body7677@naver.com</t>
+          <t>crossfit_bells@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1388-7681</t>
+          <t>0507-1424-9955</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
+          <t>대구광역시 북구 구암로21길 6 지하1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodyengineers_kr</t>
+          <t>https://cafe.naver.com/crossfitbells/5?boardType=L</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3053,13 +3053,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1442</v>
+        <v>128</v>
       </c>
       <c r="Q28" t="n">
-        <v>2051</v>
+        <v>113</v>
       </c>
       <c r="R28" t="n">
-        <v>3493</v>
+        <v>241</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,17 +3068,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1961345457</t>
+          <t>1344030973</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1961345457</t>
+          <t>https://m.place.naver.com/place/1344030973</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3090,34 +3090,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>비티비에스 PT</t>
+          <t>오짐 헬스&amp;PT 동천점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>whgudfo64@naver.com</t>
+          <t>forever7582@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1392-3331</t>
+          <t>0507-1421-9655</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 172 6층 비티비에스</t>
+          <t>대구광역시 북구 동천로 125-4 4층 오짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/whgudfo64</t>
+          <t>https://m.site.naver.com/1CMKz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3147,13 +3147,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>249</v>
+        <v>307</v>
       </c>
       <c r="Q29" t="n">
-        <v>324</v>
+        <v>657</v>
       </c>
       <c r="R29" t="n">
-        <v>573</v>
+        <v>964</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3162,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1999844382</t>
+          <t>1264751882</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999844382</t>
+          <t>https://m.place.naver.com/place/1264751882</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3184,29 +3184,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>욱스짐 도남점 헬스PT</t>
+          <t>레드워크아웃 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>thenamja89@naver.com</t>
+          <t>siytg1234@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1329-3354</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로8길 1 시그니쳐타워 7층 욱스짐</t>
+          <t>대구광역시 북구 복현로 127 4층,5층 레드워크아웃 (성화여고건너, 봄봄 건물)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wook_s_gym</t>
+          <t>https://blog.naver.com/siytg1234</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3221,7 +3217,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3241,13 +3237,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>753</v>
+        <v>255</v>
       </c>
       <c r="Q30" t="n">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="R30" t="n">
-        <v>972</v>
+        <v>496</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3252,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1340689579</t>
+          <t>1179762159</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340689579</t>
+          <t>https://m.place.naver.com/place/1179762159</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3278,29 +3274,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>사이즈핏</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>sizefitpt1989@naver.com</t>
-        </is>
-      </c>
+          <t>바른마음체육관</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1380-2027</t>
+          <t>0507-1365-0706</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 291 펫마트 2층 PT전문 사이즈핏</t>
+          <t>대구광역시 북구 동천로 156 상가 지하 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sizefitpt1989</t>
+          <t>https://www.instagram.com/brme0902?igsh=cWxxM3Y5NTRodzBi</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3315,7 +3307,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3335,13 +3327,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>182</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,51 +3342,51 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1347371484</t>
+          <t>1845136410</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1347371484</t>
+          <t>https://m.place.naver.com/place/1845136410</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>피트파크짐 PT</t>
+          <t>조지아 헬스 PT 스피닝 GX 칠곡점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>seu0112@naver.com</t>
+          <t>gogia4879@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1349-8265</t>
+          <t>0507-1383-4879</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 168 엠브로타워 4층 407호</t>
+          <t>대구광역시 북구 동천로 133 701호,702호,703호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitparkgym?igsh=MzRlODBiNWFlZA==</t>
+          <t>https://www.instagram.com/georgia.one1</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3429,13 +3421,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>47</v>
+        <v>274</v>
       </c>
       <c r="Q32" t="n">
-        <v>150</v>
+        <v>447</v>
       </c>
       <c r="R32" t="n">
-        <v>197</v>
+        <v>721</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,17 +3436,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1036478329</t>
+          <t>1013813873</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036478329</t>
+          <t>https://m.place.naver.com/place/1013813873</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3466,29 +3458,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>로이짐 1:1 PT 침산점</t>
+          <t>벨루스FIT&amp;PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ejhis12@naver.com</t>
+          <t>tizn_@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1426-1060</t>
+          <t>0507-1439-2551</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 157 4층 로이짐</t>
+          <t>대구광역시 북구 동화천로 245 6층 604호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ejhis12</t>
+          <t>https://blog.naver.com/tizn_</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3519,17 +3511,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="Q33" t="n">
-        <v>438</v>
+        <v>58</v>
       </c>
       <c r="R33" t="n">
-        <v>611</v>
+        <v>103</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,51 +3530,51 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1637712306</t>
+          <t>2076585284</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1637712306</t>
+          <t>https://m.place.naver.com/place/2076585284</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>체육관</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>필승관 레슬링 구암점</t>
+          <t>사이즈핏</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>matargear@naver.com</t>
+          <t>sizefitpt1989@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1429-2135</t>
+          <t>0507-1380-2027</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로 148 5층</t>
+          <t>대구광역시 북구 칠곡중앙대로 291 펫마트 2층 PT전문 사이즈핏</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pilseungwan_wrestling_guam</t>
+          <t>https://blog.naver.com/sizefitpt1989</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3597,7 +3589,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3617,13 +3609,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="R34" t="n">
-        <v>26</v>
+        <v>203</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3632,51 +3624,51 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1675479581</t>
+          <t>1347371484</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1675479581</t>
+          <t>https://m.place.naver.com/place/1347371484</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>더퍼스트 피트니스 칠곡점</t>
+          <t>더모스트핏</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tffpceo10@naver.com</t>
+          <t>themostfit@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1304-3714</t>
+          <t>0507-1323-4262</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 125 5층</t>
+          <t>대구광역시 북구 침산로 173 시그니처타워 7층 더모스트핏</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tffpceo10</t>
+          <t>https://www.instagram.com/themostfit_hyun</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3691,7 +3683,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3711,13 +3703,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>308</v>
+        <v>12</v>
       </c>
       <c r="Q35" t="n">
-        <v>278</v>
+        <v>25</v>
       </c>
       <c r="R35" t="n">
-        <v>586</v>
+        <v>37</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3726,17 +3718,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1040934279</t>
+          <t>1092605247</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040934279</t>
+          <t>https://m.place.naver.com/place/1092605247</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3748,29 +3740,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>대구피티클럽</t>
+          <t>포레스트짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pt9559626@naver.com</t>
+          <t>forestgym-@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>053-955-9626</t>
+          <t>0507-1482-0831</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>대구광역시 북구 서변로 65 2층</t>
+          <t>대구광역시 북구 칠성남로 43 2층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pt9559626</t>
+          <t>https://www.instagram.com/forestgym_/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3785,7 +3777,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3801,17 +3793,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Q36" t="n">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="R36" t="n">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3820,51 +3812,51 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>31383389</t>
+          <t>1186829756</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31383389</t>
+          <t>https://m.place.naver.com/place/1186829756</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>아고게퍼스널트레이닝</t>
+          <t>이지피트니스</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>yun79e@naver.com</t>
+          <t>easyfitness01@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1385-0014</t>
+          <t>0507-1350-1029</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호국로 223 부국빌딩 5층 아고게 퍼스널 트레이닝</t>
+          <t>대구광역시 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yun79e</t>
+          <t>https://blog.naver.com/easyfitness01</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3895,17 +3887,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>288</v>
       </c>
       <c r="R37" t="n">
-        <v>5</v>
+        <v>892</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3914,51 +3906,51 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>13201387</t>
+          <t>1129757069</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13201387</t>
+          <t>https://m.place.naver.com/place/1129757069</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>지젤 칠곡점 헬스 PT GX 요가</t>
+          <t>피트파크짐 PT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>giselle331704@naver.com</t>
+          <t>seu0112@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1321-6496</t>
+          <t>0507-1349-8265</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동암로 90 3층</t>
+          <t>대구광역시 북구 침산로 168 엠브로타워 4층 407호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
+          <t>https://www.instagram.com/fitparkgym?igsh=MzRlODBiNWFlZA==</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3993,13 +3985,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1241</v>
+        <v>47</v>
       </c>
       <c r="Q38" t="n">
-        <v>544</v>
+        <v>149</v>
       </c>
       <c r="R38" t="n">
-        <v>1785</v>
+        <v>196</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,17 +4000,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1616049160</t>
+          <t>1036478329</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616049160</t>
+          <t>https://m.place.naver.com/place/1036478329</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4030,29 +4022,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>메이크PT</t>
+          <t>골든피티</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>make_pt@naver.com</t>
+          <t>rhfemsvlxl@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1395-0708</t>
+          <t>0507-1344-4879</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경지묘로 2 7층</t>
+          <t>대구광역시 북구 내곡로 30 401호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/make_pt2022</t>
+          <t>https://www.instagram.com/golden.pt_</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4087,13 +4079,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="R39" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,51 +4094,51 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1709497798</t>
+          <t>1528721893</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709497798</t>
+          <t>https://m.place.naver.com/place/1528721893</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>인스타퍼스널트레이닝 PT 침산점</t>
+          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>instarpt2019@naver.com</t>
+          <t>body7677@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1345-9210</t>
+          <t>0507-1388-7681</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 165 5층 인스타퍼스널트레이닝 PT 침산점</t>
+          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/instarpt2019</t>
+          <t>https://www.instagram.com/bodyengineers_kr</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4161,7 +4153,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4181,13 +4173,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>190</v>
+        <v>1436</v>
       </c>
       <c r="Q40" t="n">
-        <v>600</v>
+        <v>2039</v>
       </c>
       <c r="R40" t="n">
-        <v>790</v>
+        <v>3475</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,51 +4188,47 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1174523938</t>
+          <t>1961345457</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174523938</t>
+          <t>https://m.place.naver.com/place/1961345457</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>지젤 노원점 헬스 PT</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>giselle331709@naver.com</t>
-        </is>
-      </c>
+          <t>크로스핏마즈</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1342-7936</t>
+          <t>0507-1311-3298</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로35길 20 5층</t>
+          <t>대구광역시 북구 침산로 144 화성투엠A동 지하1층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/giselle331709</t>
+          <t>https://www.instagram.com/marztraining</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4255,7 +4243,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4275,13 +4263,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>474</v>
+        <v>106</v>
       </c>
       <c r="Q41" t="n">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="R41" t="n">
-        <v>968</v>
+        <v>574</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,47 +4278,51 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1294730549</t>
+          <t>35720026</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294730549</t>
+          <t>https://m.place.naver.com/place/35720026</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>레드워크아웃 헬스 &amp; PT</t>
+          <t>레드짐 복싱</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>siytg1234@naver.com</t>
+          <t>dietboxing@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1420-0305</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로 127 4층,5층 레드워크아웃 (성화여고건너, 봄봄 건물)</t>
+          <t>대구광역시 북구 침산로32길 2</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/siytg1234</t>
+          <t>https://blog.naver.com/dietboxing</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4361,17 +4353,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>255</v>
+        <v>9</v>
       </c>
       <c r="Q42" t="n">
-        <v>241</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>496</v>
+        <v>10</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4380,17 +4372,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1179762159</t>
+          <t>32762709</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179762159</t>
+          <t>https://m.place.naver.com/place/32762709</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4402,34 +4394,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>스톤짐 복현점</t>
+          <t>레드짐 VIP 산격점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>stonegym_3@naver.com</t>
+          <t>redgym8555@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1333-5469</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
+          <t>대구광역시 북구 검단로 9 2층 레드맥스VIP</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pQdrxj</t>
+          <t>https://blog.naver.com/redgym8555</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4439,7 +4427,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4450,7 +4438,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4459,13 +4447,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>714</v>
+        <v>129</v>
       </c>
       <c r="Q43" t="n">
-        <v>175</v>
+        <v>89</v>
       </c>
       <c r="R43" t="n">
-        <v>889</v>
+        <v>218</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4474,56 +4462,52 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1113466448</t>
+          <t>1699698590</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113466448</t>
+          <t>https://m.place.naver.com/place/1699698590</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>체육관</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아더핏</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>rudwns5159@naver.com</t>
-        </is>
-      </c>
+          <t>필승관 레슬링 구암점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1377-5159</t>
+          <t>0507-1429-2135</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대구광역시 북구 내곡로 71 303호</t>
+          <t>대구광역시 북구 구암로 148 5층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sk9gOCze</t>
+          <t>https://www.instagram.com/pilseungwan_wrestling_guam</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4544,7 +4528,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4553,13 +4537,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q44" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4568,17 +4552,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1105478663</t>
+          <t>1675479581</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105478663</t>
+          <t>https://m.place.naver.com/place/1675479581</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4590,34 +4574,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>밸런스핏 PT&amp;필라테스</t>
+          <t>비티비에스 PT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>balancefit_pt@naver.com</t>
+          <t>whgudfo64@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1356-4983</t>
+          <t>0507-1392-3331</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 162-8 3층 밸런스핏</t>
+          <t>대구광역시 북구 침산남로 172 6층 비티비에스</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_QIETxj/chat</t>
+          <t>https://blog.naver.com/whgudfo64</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4627,7 +4611,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4638,7 +4622,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4647,13 +4631,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>64</v>
+        <v>249</v>
       </c>
       <c r="Q45" t="n">
-        <v>112</v>
+        <v>325</v>
       </c>
       <c r="R45" t="n">
-        <v>176</v>
+        <v>574</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4662,17 +4646,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1569503169</t>
+          <t>1999844382</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569503169</t>
+          <t>https://m.place.naver.com/place/1999844382</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4744,10 +4728,10 @@
         <v>155</v>
       </c>
       <c r="Q46" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="R46" t="n">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4766,41 +4750,41 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>바름PT&amp;피트니스</t>
+          <t>필라테스봄앤피티</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>baruemy@naver.com</t>
+          <t>pilatesbom8275@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1326-9724</t>
+          <t>0507-1374-8314</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경중앙로3길 21 라온하제 8층(1층에 CU있어요)</t>
+          <t>대구광역시 북구 학정로 551-50 대학당약국 건물 3층, 4층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baruemy/224250926219</t>
+          <t>https://blog.naver.com/pilatesbom8275</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4835,13 +4819,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>252</v>
+        <v>42</v>
       </c>
       <c r="Q47" t="n">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="R47" t="n">
-        <v>370</v>
+        <v>215</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4850,17 +4834,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1848126055</t>
+          <t>1470109452</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1848126055</t>
+          <t>https://m.place.naver.com/place/1470109452</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4872,34 +4856,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>오짐 헬스&amp;PT 동천점</t>
+          <t>피티명가</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>forever7582@naver.com</t>
+          <t>rhk2@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1421-9655</t>
+          <t>0507-1324-1021</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 125-4 4층 오짐 헬스&amp;PT</t>
+          <t>대구광역시 북구 침산남로 153 3층 피티명가 (정호빌딩)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://m.site.naver.com/1CMKz</t>
+          <t>http://instagram.com/ptmg153</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4929,13 +4913,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>307</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="n">
-        <v>657</v>
+        <v>34</v>
       </c>
       <c r="R48" t="n">
-        <v>964</v>
+        <v>39</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4944,51 +4928,51 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1264751882</t>
+          <t>1618018901</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264751882</t>
+          <t>https://m.place.naver.com/place/1618018901</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>심부름센터</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>대우흥신소사설탐정사무소심부름센터불륜증거미행사람찾기</t>
+          <t>바디웨이 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>koreadetective-@naver.com</t>
+          <t>striver_ocean@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>070-5253-5450</t>
+          <t>0507-1488-2098</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태전동</t>
+          <t>대구광역시 북구 구암로 148 4, 5층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/striver_ocean</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4998,12 +4982,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5023,13 +5007,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5038,17 +5022,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1223084405</t>
+          <t>1534494580</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223084405</t>
+          <t>https://m.place.naver.com/place/1534494580</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5060,25 +5044,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>더레드짐 헬스 &amp; PT</t>
+          <t>대구피티클럽</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>thered_gym@naver.com</t>
+          <t>pt9559626@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>053-955-9626</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로 105 태왕아너스상가 4층, 5층</t>
+          <t>대구광역시 북구 서변로 65 2층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/theredgym</t>
+          <t>https://blog.naver.com/pt9559626</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5093,7 +5081,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5109,17 +5097,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>472</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="R50" t="n">
-        <v>630</v>
+        <v>99</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5128,51 +5116,51 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1243559985</t>
+          <t>31383389</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243559985</t>
+          <t>https://m.place.naver.com/place/31383389</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>우아해짐헬스PT&amp;필라테스</t>
+          <t>어바웃더핏 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>tjdbs83@naver.com</t>
+          <t>mildodrax2@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1316-1135</t>
+          <t>0507-1314-2445</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 127 5층 우아해짐&amp;필라테스</t>
+          <t>대구광역시 북구 학정로 149 태전동 1195 번지 4층, 어바웃더핏</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjdbs83</t>
+          <t>https://www.instagram.com/aboutthefit_gym</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5187,7 +5175,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5198,22 +5186,22 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>86</v>
+        <v>778</v>
       </c>
       <c r="Q51" t="n">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="R51" t="n">
-        <v>313</v>
+        <v>915</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5222,17 +5210,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1145589800</t>
+          <t>1258524487</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145589800</t>
+          <t>https://m.place.naver.com/place/1258524487</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5244,29 +5232,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>골든피티</t>
+          <t>우아해짐헬스PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>rhfemsvlxl@naver.com</t>
+          <t>tjdbs83@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1344-4879</t>
+          <t>0507-1316-1135</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>대구광역시 북구 내곡로 30 401호</t>
+          <t>대구광역시 북구 동천로 127 5층 우아해짐&amp;필라테스</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/golden.pt_</t>
+          <t>https://blog.naver.com/tjdbs83</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5281,7 +5269,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5297,17 +5285,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="Q52" t="n">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="R52" t="n">
-        <v>42</v>
+        <v>317</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5316,17 +5304,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1528721893</t>
+          <t>1145589800</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1528721893</t>
+          <t>https://m.place.naver.com/place/1145589800</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5338,29 +5326,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>아트라인 퍼스널트레이닝</t>
+          <t>인스타퍼스널트레이닝 PT 침산점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>art_line_pt@naver.com</t>
+          <t>instarpt2019@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1369-2929</t>
+          <t>0507-1345-9210</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로 206 2, 3층</t>
+          <t>대구광역시 북구 침산남로 165 5층 인스타퍼스널트레이닝 PT 침산점</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/art_line_pt</t>
+          <t>https://blog.naver.com/instarpt2019</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5395,13 +5383,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="Q53" t="n">
-        <v>169</v>
+        <v>604</v>
       </c>
       <c r="R53" t="n">
-        <v>252</v>
+        <v>796</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5410,17 +5398,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>34079230</t>
+          <t>1174523938</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34079230</t>
+          <t>https://m.place.naver.com/place/1174523938</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5432,34 +5420,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>피트낸스코리아</t>
+          <t>밸런스핏 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>enrqorl88@naver.com</t>
+          <t>balancefit_pt@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1600-7178</t>
+          <t>0507-1356-4983</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 180</t>
+          <t>대구광역시 북구 침산로 162-8 3층 밸런스핏</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://fitnance.kr</t>
+          <t>http://pf.kakao.com/_QIETxj/chat</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5480,22 +5468,22 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5504,51 +5492,43 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1785367820</t>
+          <t>1569503169</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785367820</t>
+          <t>https://m.place.naver.com/place/1569503169</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>피트온24 칠곡점</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>fitness240@naver.com</t>
-        </is>
-      </c>
+          <t>모야짐</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>053-313-8817</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 416 4층 피트온24</t>
+          <t>대구광역시 북구 칠성로 25-22 모야짐</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitness240</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5558,12 +5538,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5574,22 +5554,22 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2309</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>976</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>3285</v>
+        <v>6</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5598,17 +5578,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1175448883</t>
+          <t>1763678127</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1175448883</t>
+          <t>https://m.place.naver.com/place/1763678127</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5620,29 +5600,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>마이송 피트니스</t>
+          <t>점핑하이 칠곡점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>dzosel@naver.com</t>
+          <t>pkl0314@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1364-7153</t>
+          <t>0507-1318-0956</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 247 상가동 211호</t>
+          <t>대구광역시 북구 동천로23길 2 골든프라자 7층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/jumping51130956</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5652,7 +5632,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5673,17 +5653,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="R56" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5692,17 +5672,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1435987015</t>
+          <t>1136410767</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1435987015</t>
+          <t>https://m.place.naver.com/place/1136410767</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5714,29 +5694,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>에이블리 PT센터</t>
+          <t>국민피티 침산점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>tlsrms321@naver.com</t>
+          <t>kukminpt@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1321-0018</t>
+          <t>0507-1398-9797</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 527 3층</t>
+          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ably_ptct</t>
+          <t>https://www.instagram.com/kukminpt</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5771,13 +5751,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>34</v>
+        <v>702</v>
       </c>
       <c r="Q57" t="n">
-        <v>102</v>
+        <v>1022</v>
       </c>
       <c r="R57" t="n">
-        <v>136</v>
+        <v>1724</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5786,17 +5766,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1508796529</t>
+          <t>1636758988</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1508796529</t>
+          <t>https://m.place.naver.com/place/1636758988</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5808,29 +5788,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>아이디짐 헬스&amp;PT</t>
+          <t>바디채널 침산점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ildomin@naver.com</t>
+          <t>bodycs@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1319-9446</t>
+          <t>0507-1342-4850</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대구광역시 북구 내곡로 73 금강프라자 3층 아이디헬스IDGYM</t>
+          <t>대구광역시 북구 침산남로 154 10층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/idgym24h?igsh=MTBnOHl0a2M3enBxdQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/bodychannel_chimsan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5856,7 +5836,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5865,13 +5845,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="Q58" t="n">
-        <v>135</v>
+        <v>1529</v>
       </c>
       <c r="R58" t="n">
-        <v>209</v>
+        <v>1706</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5880,17 +5860,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1254581921</t>
+          <t>1023076989</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1254581921</t>
+          <t>https://m.place.naver.com/place/1023076989</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5902,29 +5882,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>점핑하이 칠곡점</t>
+          <t>마이송 피트니스</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>pkl0314@naver.com</t>
+          <t>dzosel@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1318-0956</t>
+          <t>0507-1364-7153</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 2 골든프라자 7층</t>
+          <t>대구광역시 북구 동북로 247 상가동 211호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://instagram.com/jumping51130956</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5934,7 +5914,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5955,17 +5935,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q59" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5974,51 +5954,51 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1136410767</t>
+          <t>1435987015</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136410767</t>
+          <t>https://m.place.naver.com/place/1435987015</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>조지아 헬스 PT 스피닝 GX 칠곡점</t>
+          <t>딜라이트 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>gogia4879@naver.com</t>
+          <t>delight_pt@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1383-4879</t>
+          <t>0507-1327-2806</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 133 701호,702호,703호</t>
+          <t>대구광역시 북구 매천로 124 2층 딜라이트 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/georgia.one1</t>
+          <t>https://blog.naver.com/delight_pt</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6033,7 +6013,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6053,13 +6033,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>273</v>
+        <v>114</v>
       </c>
       <c r="Q60" t="n">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="R60" t="n">
-        <v>719</v>
+        <v>135</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6068,17 +6048,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1013813873</t>
+          <t>1922976757</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013813873</t>
+          <t>https://m.place.naver.com/place/1922976757</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6090,29 +6070,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>그린짐</t>
+          <t>엔드짐</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>pk0236@naver.com</t>
+          <t>himy491@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1390-5563</t>
+          <t>053-311-6939</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 439 502호</t>
+          <t>대구광역시 북구 매천로18길 29 5층, 엔드짐</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/endgym_official</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6122,7 +6102,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6143,17 +6123,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R61" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6162,17 +6142,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1007068851</t>
+          <t>1314145805</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1007068851</t>
+          <t>https://m.place.naver.com/place/1314145805</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6184,29 +6164,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>레드짐 침산점 헬스&amp;스파</t>
+          <t>피트온24 칠곡점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>redgym-chim@naver.com</t>
+          <t>fitness240@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1329-5605</t>
+          <t>053-313-8817</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 138 6층</t>
+          <t>대구광역시 북구 학정로 416 4층 피트온24</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/redgym_chimsan</t>
+          <t>https://blog.naver.com/fitness240</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6221,7 +6201,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6232,7 +6212,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6241,13 +6221,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>394</v>
+        <v>2309</v>
       </c>
       <c r="Q62" t="n">
-        <v>224</v>
+        <v>977</v>
       </c>
       <c r="R62" t="n">
-        <v>618</v>
+        <v>3286</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6256,17 +6236,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1070126824</t>
+          <t>1175448883</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070126824</t>
+          <t>https://m.place.naver.com/place/1175448883</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6278,29 +6258,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>더모스트핏</t>
+          <t>피트낸스코리아</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>themostfit@naver.com</t>
+          <t>enrqorl88@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1323-4262</t>
+          <t>1600-7178</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 173 시그니처타워 7층 더모스트핏</t>
+          <t>대구광역시 북구 칠곡중앙대로 180</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/themostfit_hyun</t>
+          <t>http://fitnance.kr</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6331,17 +6311,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6350,17 +6330,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1092605247</t>
+          <t>1785367820</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092605247</t>
+          <t>https://m.place.naver.com/place/1785367820</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6372,34 +6352,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>바디채널 침산점</t>
+          <t>레드짐 복현오거리점 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bodycs@naver.com</t>
+          <t>redgym8555@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1342-4850</t>
+          <t>053-1877-3632</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 154 10층</t>
+          <t>대구광역시 북구 검단로 9 3층, 4층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodychannel_chimsan</t>
+          <t>https://litt.ly/redgym_b5</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6429,13 +6409,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>177</v>
+        <v>818</v>
       </c>
       <c r="Q64" t="n">
-        <v>1529</v>
+        <v>657</v>
       </c>
       <c r="R64" t="n">
-        <v>1706</v>
+        <v>1475</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6444,51 +6424,51 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1023076989</t>
+          <t>1813814971</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023076989</t>
+          <t>https://m.place.naver.com/place/1813814971</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>제이에스타운 퍼스널트레이닝센터</t>
+          <t>더퍼스트 피트니스 칠곡점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>dran77@naver.com</t>
+          <t>tffpceo10@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>053-354-9797</t>
+          <t>0507-1304-3714</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>대구광역시 북구 옥산로 98 2F</t>
+          <t>대구광역시 북구 동천로 125 5층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/tffpceo10</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6498,12 +6478,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6519,17 +6499,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>12</v>
+        <v>309</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>278</v>
       </c>
       <c r="R65" t="n">
-        <v>17</v>
+        <v>587</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6538,51 +6518,51 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1094798598</t>
+          <t>1040934279</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1094798598</t>
+          <t>https://m.place.naver.com/place/1040934279</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>필라테스봄앤피티</t>
+          <t>로이짐 1:1 PT 침산점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>pilatesbom8275@naver.com</t>
+          <t>ejhis12@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1374-8314</t>
+          <t>0507-1426-1060</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 551-50 대학당약국 건물 3층, 4층</t>
+          <t>대구광역시 북구 침산남로 157 4층 로이짐</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilatesbom8275</t>
+          <t>https://blog.naver.com/ejhis12</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6617,13 +6597,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="Q66" t="n">
-        <v>173</v>
+        <v>439</v>
       </c>
       <c r="R66" t="n">
-        <v>215</v>
+        <v>612</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6632,17 +6612,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1470109452</t>
+          <t>1637712306</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1470109452</t>
+          <t>https://m.place.naver.com/place/1637712306</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6654,29 +6634,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>슬릭부스트 대구칠곡캠프</t>
+          <t>빅토리짐 PT&amp;헬스 동천점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ajdajddl5@naver.com</t>
+          <t>sjsjfit@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>053-326-5563</t>
+          <t>0507-1370-1301</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 439 503호</t>
+          <t>대구광역시 북구 동천로23길 36 2층 201호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sjsjfit</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6686,12 +6666,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6707,17 +6687,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="Q67" t="n">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="R67" t="n">
-        <v>107</v>
+        <v>292</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6726,47 +6706,51 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1817392005</t>
+          <t>1903714032</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817392005</t>
+          <t>https://m.place.naver.com/place/1903714032</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>레드짐 VIP 산격점</t>
+          <t>지젤 노원점 헬스 PT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>redgym8555@naver.com</t>
+          <t>giselle331709@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1342-7936</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>대구광역시 북구 검단로 9 2층 레드맥스VIP</t>
+          <t>대구광역시 북구 팔달로35길 20 5층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/redgym8555</t>
+          <t>https://blog.naver.com/giselle331709</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6801,13 +6785,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>129</v>
+        <v>475</v>
       </c>
       <c r="Q68" t="n">
-        <v>89</v>
+        <v>495</v>
       </c>
       <c r="R68" t="n">
-        <v>218</v>
+        <v>970</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6816,17 +6800,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1699698590</t>
+          <t>1294730549</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699698590</t>
+          <t>https://m.place.naver.com/place/1294730549</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6838,29 +6822,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>이지피트니스</t>
+          <t>그린짐</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>easyfitness01@naver.com</t>
+          <t>30755@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1350-1029</t>
+          <t>0507-1390-5563</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
+          <t>대구광역시 북구 학정로 439 502호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/easyfitness01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6870,12 +6854,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6891,17 +6875,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>605</v>
+        <v>23</v>
       </c>
       <c r="Q69" t="n">
-        <v>286</v>
+        <v>5</v>
       </c>
       <c r="R69" t="n">
-        <v>891</v>
+        <v>28</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6910,17 +6894,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1129757069</t>
+          <t>1007068851</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129757069</t>
+          <t>https://m.place.naver.com/place/1007068851</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6932,34 +6916,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>스프라우트핏 여성전용 헬스&amp;PT</t>
+          <t>매드짐</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sproutfit_@naver.com</t>
+          <t>csd828282@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0507-1402-8161</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 10 4층</t>
+          <t>대구광역시 북구 연경지묘로 6 센텀타워 8층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_Kpyxin?fbclid</t>
+          <t>https://blog.naver.com/csd828282</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6969,7 +6949,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6980,7 +6960,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6989,13 +6969,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="Q70" t="n">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="R70" t="n">
-        <v>203</v>
+        <v>32</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7004,51 +6984,47 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2039687494</t>
+          <t>1036138674</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039687494</t>
+          <t>https://m.place.naver.com/place/1036138674</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>레드짐 복싱</t>
+          <t>더레드짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>dietboxing@naver.com</t>
+          <t>thered_gym@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1420-0305</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로32길 2</t>
+          <t>대구광역시 북구 복현로 105 태왕아너스상가 4층, 5층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dietboxing</t>
+          <t>https://www.instagram.com/theredgym</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7063,7 +7039,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7079,17 +7055,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>9</v>
+        <v>474</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="R71" t="n">
-        <v>10</v>
+        <v>632</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7098,56 +7074,56 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>32762709</t>
+          <t>1243559985</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32762709</t>
+          <t>https://m.place.naver.com/place/1243559985</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>레드짐 복현오거리점 헬스 &amp; PT</t>
+          <t>더피지오랩 PT &amp; 재활 센터</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>redgym8555@naver.com</t>
+          <t>thephysiolab@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>053-1877-3632</t>
+          <t>0507-1372-7079</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>대구광역시 북구 검단로 9 3층, 4층</t>
+          <t>대구광역시 북구 옥산로 95 205호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://litt.ly/redgym_b5</t>
+          <t>https://blog.naver.com/thephysiolab</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7157,7 +7133,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7177,13 +7153,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>816</v>
+        <v>53</v>
       </c>
       <c r="Q72" t="n">
-        <v>662</v>
+        <v>46</v>
       </c>
       <c r="R72" t="n">
-        <v>1478</v>
+        <v>99</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7192,17 +7168,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1813814971</t>
+          <t>1267989266</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1813814971</t>
+          <t>https://m.place.naver.com/place/1267989266</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7214,29 +7190,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>빅토리짐 PT&amp;헬스 동천점</t>
+          <t>스타트 PT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>sjsjfit@naver.com</t>
+          <t>startpt6260@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1370-1301</t>
+          <t>0507-1374-6260</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 36 2층 201호</t>
+          <t>대구광역시 북구 대현남로 41 3층 302호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sjsjfit</t>
+          <t>https://www.instagram.com/start_pt6260</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7251,7 +7227,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7271,13 +7247,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="Q73" t="n">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="R73" t="n">
-        <v>292</v>
+        <v>46</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7286,17 +7262,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1903714032</t>
+          <t>1981809419</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1903714032</t>
+          <t>https://m.place.naver.com/place/1981809419</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7308,29 +7284,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>바디웨이 헬스&amp;PT</t>
+          <t>욱스짐 도남점 헬스PT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>striver_ocean@naver.com</t>
+          <t>thenamja89@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1488-2098</t>
+          <t>0507-1329-3354</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로 148 4, 5층</t>
+          <t>대구광역시 북구 도남중앙로8길 1 시그니쳐타워 7층 욱스짐</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/striver_ocean</t>
+          <t>https://www.instagram.com/wook_s_gym</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7345,7 +7321,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7361,17 +7337,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>73</v>
+        <v>757</v>
       </c>
       <c r="Q74" t="n">
-        <v>76</v>
+        <v>222</v>
       </c>
       <c r="R74" t="n">
-        <v>149</v>
+        <v>979</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7380,17 +7356,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1534494580</t>
+          <t>1340689579</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1534494580</t>
+          <t>https://m.place.naver.com/place/1340689579</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7402,29 +7378,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JH스포츠재활센터</t>
+          <t>침산동 그룹PT 운동하는코끼리</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>toughwogh@naver.com</t>
+          <t>oosotoo@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>053-325-2132</t>
+          <t>0507-1403-3006</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대천로 93 덕영빌딩 5층 501호</t>
+          <t>대구광역시 북구 침산남로 172 3층 운동하는 코끼리</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/toughwogh</t>
+          <t>https://blog.naver.com/oosotoo</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7455,17 +7431,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="R75" t="n">
-        <v>2</v>
+        <v>343</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7474,51 +7450,51 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>33666439</t>
+          <t>36123882</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33666439</t>
+          <t>https://m.place.naver.com/place/36123882</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>국민피티 침산점</t>
+          <t>피트온24 복현점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kukminpt@naver.com</t>
+          <t>mave000@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1398-9797</t>
+          <t>0507-1322-3225</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kukminpt</t>
+          <t>https://blog.naver.com/mave000</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7533,7 +7509,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7553,13 +7529,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>701</v>
+        <v>2032</v>
       </c>
       <c r="Q76" t="n">
-        <v>1015</v>
+        <v>980</v>
       </c>
       <c r="R76" t="n">
-        <v>1716</v>
+        <v>3012</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7568,17 +7544,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1636758988</t>
+          <t>1855565865</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636758988</t>
+          <t>https://m.place.naver.com/place/1855565865</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
